--- a/figures_updated/Fig7_stats.xlsx
+++ b/figures_updated/Fig7_stats.xlsx
@@ -485,16 +485,16 @@
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000531912663444839</v>
+        <v>0.000588460097464455</v>
       </c>
       <c r="F2" t="n">
-        <v>0.267700431953138</v>
+        <v>0.252893879514037</v>
       </c>
       <c r="G2" t="n">
-        <v>0.270112423702978</v>
+        <v>0.255060689697766</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E3" t="n">
-        <v>0.518541051640422</v>
+        <v>0.618107430715854</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0107664056277532</v>
+        <v>0.0061174106228956</v>
       </c>
       <c r="G3" t="n">
-        <v>0.270112423702978</v>
+        <v>0.255060689697766</v>
       </c>
     </row>
     <row r="4">
@@ -534,13 +534,13 @@
         <v>53</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000742404319250132</v>
+        <v>0.000109232094438822</v>
       </c>
       <c r="F4" t="n">
-        <v>0.201717712314739</v>
+        <v>0.256472422966226</v>
       </c>
       <c r="G4" t="n">
-        <v>0.317344194087766</v>
+        <v>0.356877109863101</v>
       </c>
     </row>
     <row r="5">
@@ -557,13 +557,13 @@
         <v>53</v>
       </c>
       <c r="E5" t="n">
-        <v>0.379037601261171</v>
+        <v>0.879464880707709</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0152054542337827</v>
+        <v>0.000455259940258539</v>
       </c>
       <c r="G5" t="n">
-        <v>0.317344194087766</v>
+        <v>0.356877109863101</v>
       </c>
     </row>
   </sheetData>
@@ -605,16 +605,16 @@
         <v>22</v>
       </c>
       <c r="C2" t="n">
-        <v>30.2071768272923</v>
+        <v>29.6864121448192</v>
       </c>
       <c r="D2" t="n">
-        <v>10.2742601968896</v>
+        <v>9.87060875891045</v>
       </c>
       <c r="E2" t="n">
-        <v>2.94008291092697</v>
+        <v>3.00755635948193</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00562725080017343</v>
+        <v>0.00459327717812685</v>
       </c>
     </row>
     <row r="3">
@@ -625,16 +625,16 @@
         <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.710349117181877</v>
+        <v>-0.659474666025366</v>
       </c>
       <c r="D3" t="n">
-        <v>0.193148275978945</v>
+        <v>0.181504668836867</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.67773987927964</v>
+        <v>-3.63337577072516</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000743491421008671</v>
+        <v>0.000805254478387591</v>
       </c>
     </row>
     <row r="4">
@@ -645,16 +645,16 @@
         <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>0.133022159296779</v>
+        <v>0.10130892718089</v>
       </c>
       <c r="D4" t="n">
-        <v>0.209622159424547</v>
+        <v>0.206775527688258</v>
       </c>
       <c r="E4" t="n">
-        <v>0.634580617153981</v>
+        <v>0.489946408617691</v>
       </c>
       <c r="F4" t="n">
-        <v>0.529606508514629</v>
+        <v>0.62691674399311</v>
       </c>
     </row>
     <row r="5">
@@ -665,16 +665,16 @@
         <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>-6.63587992932028</v>
+        <v>-5.88064924814376</v>
       </c>
       <c r="D5" t="n">
-        <v>5.63200921239063</v>
+        <v>5.67889205911633</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.17824379880649</v>
+        <v>-1.03552756187777</v>
       </c>
       <c r="F5" t="n">
-        <v>0.246221957265634</v>
+        <v>0.30680107658486</v>
       </c>
     </row>
     <row r="6">
@@ -685,16 +685,16 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>-11.9156729219777</v>
+        <v>-9.89374070811195</v>
       </c>
       <c r="D6" t="n">
-        <v>6.64141837435611</v>
+        <v>6.57790176357389</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.79414580596015</v>
+        <v>-1.50408763519395</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0789608835484214</v>
+        <v>0.138977560289022</v>
       </c>
     </row>
     <row r="7">
@@ -705,16 +705,16 @@
         <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>0.345397138291106</v>
+        <v>0.419516522536063</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0981582765537473</v>
+        <v>0.102042063685039</v>
       </c>
       <c r="E7" t="n">
-        <v>3.51877753377201</v>
+        <v>4.11121166493588</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000946499377099306</v>
+        <v>0.000149589682819267</v>
       </c>
     </row>
     <row r="8">
@@ -725,16 +725,16 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>0.118260664435437</v>
+        <v>0.0211695013612778</v>
       </c>
       <c r="D8" t="n">
-        <v>0.135961326406756</v>
+        <v>0.141704613221401</v>
       </c>
       <c r="E8" t="n">
-        <v>0.869811052605032</v>
+        <v>0.149391758532253</v>
       </c>
       <c r="F8" t="n">
-        <v>0.388644741586922</v>
+        <v>0.881857705715996</v>
       </c>
     </row>
     <row r="9">
@@ -745,16 +745,16 @@
         <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.4644596773417</v>
+        <v>-7.07066744834295</v>
       </c>
       <c r="D9" t="n">
-        <v>3.78377665832779</v>
+        <v>3.73796182049639</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.44418134863083</v>
+        <v>-1.89158364581798</v>
       </c>
       <c r="F9" t="n">
-        <v>0.155052084713326</v>
+        <v>0.0644645582721118</v>
       </c>
     </row>
   </sheetData>
@@ -814,40 +814,40 @@
         <v>21</v>
       </c>
       <c r="B2" t="n">
-        <v>0.270112423702978</v>
+        <v>0.255060689697766</v>
       </c>
       <c r="C2" t="n">
-        <v>0.210932349949165</v>
+        <v>0.197757665828364</v>
       </c>
       <c r="D2" t="n">
-        <v>2.58189803672588</v>
+        <v>2.55442922279978</v>
       </c>
       <c r="E2" t="n">
-        <v>4.56424614857084</v>
+        <v>4.4510860417954</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00809480381880257</v>
+        <v>0.00878172559831409</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>-94.961586569098</v>
+        <v>-99.2417683411628</v>
       </c>
       <c r="I2" t="n">
-        <v>199.923173138196</v>
+        <v>208.483536682326</v>
       </c>
       <c r="J2" t="n">
-        <v>208.491033471718</v>
+        <v>217.289537260793</v>
       </c>
       <c r="K2" t="n">
-        <v>246.649306465812</v>
+        <v>254.479237517446</v>
       </c>
       <c r="L2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -855,34 +855,34 @@
         <v>24</v>
       </c>
       <c r="B3" t="n">
-        <v>0.317344194087766</v>
+        <v>0.356877109863101</v>
       </c>
       <c r="C3" t="n">
-        <v>0.275548940664568</v>
+        <v>0.317502239038393</v>
       </c>
       <c r="D3" t="n">
-        <v>1.87937936345749</v>
+        <v>1.90798264779767</v>
       </c>
       <c r="E3" t="n">
-        <v>7.59282856535158</v>
+        <v>9.06357538166594</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000288141035260003</v>
+        <v>0.0000704170221783352</v>
       </c>
       <c r="G3" t="n">
         <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>-106.564149066094</v>
+        <v>-107.364707813219</v>
       </c>
       <c r="I3" t="n">
-        <v>223.128298132188</v>
+        <v>224.729415626438</v>
       </c>
       <c r="J3" t="n">
-        <v>232.979757699948</v>
+        <v>234.580875194199</v>
       </c>
       <c r="K3" t="n">
-        <v>173.071272797703</v>
+        <v>178.379491430554</v>
       </c>
       <c r="L3" t="n">
         <v>49</v>
@@ -921,7 +921,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>1.116</v>
+        <v>1.204</v>
       </c>
     </row>
     <row r="3">
@@ -932,7 +932,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>1.109</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="4">
@@ -943,7 +943,7 @@
         <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>1.115</v>
+        <v>1.189</v>
       </c>
     </row>
     <row r="5">
@@ -954,7 +954,7 @@
         <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>1.119</v>
+        <v>1.098</v>
       </c>
     </row>
     <row r="6">
@@ -965,7 +965,7 @@
         <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>1.094</v>
+        <v>1.142</v>
       </c>
     </row>
     <row r="7">
@@ -976,7 +976,7 @@
         <v>23</v>
       </c>
       <c r="C7" t="n">
-        <v>1.175</v>
+        <v>1.132</v>
       </c>
     </row>
   </sheetData>
